--- a/artfynd/A 13652-2026 artfynd.xlsx
+++ b/artfynd/A 13652-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131757135</v>
       </c>
       <c r="B2" t="n">
-        <v>96343</v>
+        <v>96346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13652-2026 artfynd.xlsx
+++ b/artfynd/A 13652-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131757135</v>
       </c>
       <c r="B2" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13652-2026 artfynd.xlsx
+++ b/artfynd/A 13652-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131757135</v>
       </c>
       <c r="B2" t="n">
-        <v>96406</v>
+        <v>96501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
